--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487184_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487184_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3203</v>
+        <v>3.0189</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0765</v>
+        <v>2.6948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2438</v>
+        <v>0.3241</v>
       </c>
       <c r="G2" t="n">
         <v>2.2829</v>
@@ -610,13 +610,13 @@
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7925</v>
+        <v>-1.0939</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6954</v>
+        <v>0.3137</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4879</v>
+        <v>-1.4076</v>
       </c>
       <c r="V2" t="n">
         <v>0.2859</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6986</v>
+        <v>2.879</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0491</v>
+        <v>7.1492</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.3505</v>
+        <v>-4.2702</v>
       </c>
       <c r="G3" t="n">
         <v>2.7536</v>
@@ -688,13 +688,13 @@
         <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.283</v>
+        <v>-1.1025</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0912</v>
+        <v>0.0089</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1918</v>
+        <v>-1.1115</v>
       </c>
       <c r="V3" t="n">
         <v>1.228</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. DIEZ TIDALA</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5265</v>
+        <v>1.6073</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7932</v>
+        <v>2.6593</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2667</v>
+        <v>-1.052</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0172</v>
+        <v>1.9843</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0918</v>
+        <v>1.6259</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0746</v>
+        <v>0.3584</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6364</v>
+        <v>4.7197</v>
       </c>
       <c r="K4" t="n">
-        <v>1.304</v>
+        <v>2.0335</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6676</v>
+        <v>2.6861</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3807</v>
+        <v>-2.7353</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7877</v>
+        <v>-0.4076</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.407</v>
+        <v>-2.3277</v>
       </c>
       <c r="P4" t="n">
-        <v>0.386</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.0881</v>
       </c>
       <c r="R4" t="n">
-        <v>0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4092</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1567</v>
+        <v>-0.158</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7476</v>
+        <v>-0.5169</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2859</v>
+        <v>1.842</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1857</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3343</v>
+        <v>1.487</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1165</v>
+        <v>0.3763</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2178</v>
+        <v>1.1107</v>
       </c>
       <c r="G5" t="n">
         <v>2.0763</v>
@@ -844,13 +844,13 @@
         <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8421</v>
+        <v>-0.6894</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2974</v>
+        <v>-0.0377</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5447</v>
+        <v>-0.6518</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2859</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>L. DIEZ TIDALA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1612</v>
+        <v>1.1249</v>
       </c>
       <c r="E6" t="n">
-        <v>1.999</v>
+        <v>1.3113</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8378</v>
+        <v>-0.1864</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9843</v>
+        <v>1.0172</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6259</v>
+        <v>2.0918</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3584</v>
+        <v>-1.0746</v>
       </c>
       <c r="J6" t="n">
-        <v>4.7197</v>
+        <v>0.6364</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0335</v>
+        <v>1.304</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6861</v>
+        <v>-0.6676</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7353</v>
+        <v>0.3807</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4076</v>
+        <v>0.7877</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.3277</v>
+        <v>-0.407</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0881</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1211</v>
+        <v>0.0076</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8183</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3028</v>
+        <v>-0.6673</v>
       </c>
       <c r="V6" t="n">
-        <v>1.842</v>
+        <v>-0.2859</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6562</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5364</v>
+        <v>0.59</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0188</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5552</v>
+        <v>0.6088</v>
       </c>
       <c r="G7" t="n">
         <v>0.1742</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0238</v>
+        <v>0.0297</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0208</v>
+        <v>-0.2615</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.402</v>
+        <v>-1.4241</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3812</v>
+        <v>1.1626</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.4915</v>
+        <v>-1.2082</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2317</v>
+        <v>1.0288</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.7232</v>
+        <v>-2.237</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7101</v>
+        <v>-1.1358</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5058</v>
+        <v>0.1344</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2159</v>
+        <v>-1.2702</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7814</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2741</v>
+        <v>0.8944</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5073</v>
+        <v>-0.9668</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8844</v>
+        <v>-1.2463</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6941000000000001</v>
+        <v>-0.3582</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1903</v>
+        <v>-0.8881</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6948</v>
+        <v>-0.8239</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8842</v>
+        <v>-1.8839</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1894</v>
+        <v>1.06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2082</v>
+        <v>-3.4915</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0288</v>
+        <v>1.2317</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.237</v>
+        <v>-4.7232</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1358</v>
+        <v>-1.7101</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1344</v>
+        <v>1.5058</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2702</v>
+        <v>-3.2159</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-1.7814</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8944</v>
+        <v>-0.2741</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9668</v>
+        <v>-1.5073</v>
       </c>
       <c r="P9" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.158</v>
+        <v>-0.386</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1231</v>
+        <v>2.3161</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6796</v>
+        <v>0.0813</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8183</v>
+        <v>0.2122</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8613</v>
+        <v>-0.1309</v>
       </c>
       <c r="V9" t="n">
-        <v>1.228</v>
+        <v>0.6562</v>
       </c>
       <c r="W9" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7691</v>
+        <v>-1.5371</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2131</v>
+        <v>-0.0346</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.556</v>
+        <v>-1.5024</v>
       </c>
       <c r="G10" t="n">
         <v>1.107</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.285</v>
+        <v>-1.053</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0278</v>
+        <v>0.2062</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3128</v>
+        <v>-1.2592</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1701</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8803</v>
+        <v>-5.5402</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5725</v>
+        <v>-4.5537</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3077</v>
+        <v>-0.9865</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3418</v>
@@ -1312,13 +1312,13 @@
         <v>2.5091</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5155</v>
+        <v>-0.1755</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1048</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6015</v>
+        <v>-0.2803</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2859</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6021</v>
+        <v>-6.0419</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3274</v>
+        <v>-1.7673</v>
       </c>
       <c r="F12" t="n">
         <v>-4.2746</v>
@@ -1390,10 +1390,10 @@
         <v>0.193</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2466</v>
+        <v>-0.6864</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5949</v>
+        <v>-0.0347</v>
       </c>
       <c r="U12" t="n">
         <v>-0.6518</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.389800000000001</v>
+        <v>-3.4975</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6163</v>
+        <v>4.508500000000003</v>
       </c>
       <c r="F13" t="n">
         <v>-8.0059</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7402999999999991</v>
+        <v>0.7403000000000008</v>
       </c>
       <c r="H13" t="n">
         <v>16.2239</v>
@@ -1468,10 +1468,10 @@
         <v>14.4757</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.4956</v>
+        <v>-6.6033</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.01959999999999973</v>
+        <v>0.8726</v>
       </c>
       <c r="U13" t="n">
         <v>-7.4762</v>
@@ -1480,7 +1480,7 @@
         <v>-0.5294999999999996</v>
       </c>
       <c r="W13" t="n">
-        <v>6.3413</v>
+        <v>6.341299999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-6.870800000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.413399999999999</v>
+        <v>10.6683</v>
       </c>
       <c r="E14" t="n">
-        <v>8.6281</v>
+        <v>9.829800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7853</v>
+        <v>0.8385</v>
       </c>
       <c r="G14" t="n">
         <v>8.136900000000001</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5123</v>
+        <v>0.7426</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7297</v>
+        <v>0.472</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2174</v>
+        <v>0.2706</v>
       </c>
       <c r="V14" t="n">
         <v>4.2979</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9198</v>
+        <v>2.8492</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9066</v>
+        <v>3.1041</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0131</v>
+        <v>-0.2549</v>
       </c>
       <c r="G15" t="n">
         <v>0.9115</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2905</v>
+        <v>2.2199</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6328</v>
+        <v>1.8303</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6576</v>
+        <v>0.3896</v>
       </c>
       <c r="V15" t="n">
         <v>-2.2123</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6068</v>
+        <v>1.2016</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7394</v>
+        <v>1.4312</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1326</v>
+        <v>-0.2296</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9443</v>
+        <v>0.8526</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3381</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3938</v>
+        <v>0.7718</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2767</v>
+        <v>1.7068</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0092</v>
+        <v>1.0557</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7326</v>
+        <v>0.6512</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6677</v>
+        <v>-0.8542</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3288</v>
+        <v>-0.9749</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6612</v>
+        <v>0.1207</v>
       </c>
       <c r="P16" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0649</v>
+        <v>-0.23</v>
       </c>
       <c r="T16" t="n">
-        <v>2.016</v>
+        <v>-0.2756</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0489</v>
+        <v>0.0456</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9478</v>
+        <v>0.3982</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2309</v>
+        <v>0.6378</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2832</v>
+        <v>-0.2397</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8526</v>
+        <v>-0.9443</v>
       </c>
       <c r="H17" t="n">
-        <v>0.08069999999999999</v>
+        <v>-2.3381</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7718</v>
+        <v>1.3938</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7068</v>
+        <v>-0.2767</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0557</v>
+        <v>-1.0092</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6512</v>
+        <v>0.7326</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8542</v>
+        <v>-0.6677</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9749</v>
+        <v>-1.3288</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1207</v>
+        <v>0.6612</v>
       </c>
       <c r="P17" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4838</v>
+        <v>0.8563</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4759</v>
+        <v>0.9145</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0582</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.837</v>
+        <v>0.3518</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1777</v>
+        <v>-0.1763</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3407</v>
+        <v>0.5281</v>
       </c>
       <c r="G18" t="n">
         <v>-0.65</v>
@@ -1858,13 +1858,13 @@
         <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1521</v>
+        <v>0.0367</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5949</v>
+        <v>0.4065</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5572</v>
+        <v>-0.3698</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8423</v>
+        <v>-0.6423</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8004</v>
+        <v>-0.6001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0419</v>
+        <v>-0.0422</v>
       </c>
       <c r="G19" t="n">
         <v>0.0638</v>
@@ -1936,13 +1936,13 @@
         <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0543</v>
+        <v>1.2542</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2004</v>
+        <v>1.4007</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1461</v>
+        <v>-0.1464</v>
       </c>
       <c r="V19" t="n">
         <v>1.5138</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8718</v>
+        <v>-1.2611</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4493</v>
+        <v>2.2468</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5775</v>
+        <v>-3.5078</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5543</v>
+        <v>-1.1687</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9955</v>
+        <v>-0.384</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4413</v>
+        <v>-0.7847</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9414</v>
+        <v>0.5194</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9821</v>
+        <v>0.4709</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>0.0486</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3871</v>
+        <v>-1.6881</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0134</v>
+        <v>-0.8548</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4006</v>
+        <v>-0.8333</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.772</v>
+        <v>-0.193</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1686</v>
+        <v>1.0427</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1713</v>
+        <v>0.8927</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0026</v>
+        <v>0.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2859</v>
+        <v>-0.9421</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2859</v>
+        <v>1.7997</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3658</v>
+        <v>-1.4657</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3469</v>
+        <v>-2.1503</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.7127</v>
+        <v>0.6846</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1687</v>
+        <v>-1.5543</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.384</v>
+        <v>-1.9955</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7847</v>
+        <v>0.4413</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5194</v>
+        <v>-1.9414</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4709</v>
+        <v>-1.9821</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0486</v>
+        <v>0.0407</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6881</v>
+        <v>0.3871</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8548</v>
+        <v>-0.0134</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8333</v>
+        <v>0.4006</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9379</v>
+        <v>0.5747</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9928</v>
+        <v>0.4703</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0549</v>
+        <v>0.1044</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9421</v>
+        <v>0.2859</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7997</v>
+        <v>0.2859</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.7418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0372</v>
+        <v>-1.9232</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0838</v>
+        <v>-1.1839</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9534</v>
+        <v>-0.7393</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8562</v>
@@ -2170,13 +2170,13 @@
         <v>0.386</v>
       </c>
       <c r="S22" t="n">
-        <v>0.661</v>
+        <v>0.775</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8593</v>
+        <v>0.7592</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1983</v>
+        <v>0.0159</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2158</v>
+        <v>-2.0284</v>
       </c>
       <c r="E23" t="n">
         <v>-2.4665</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2507</v>
+        <v>0.4381</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6588000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>0.579</v>
       </c>
       <c r="S23" t="n">
-        <v>0.08</v>
+        <v>0.2674</v>
       </c>
       <c r="T23" t="n">
         <v>0.0291</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0509</v>
+        <v>0.2383</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2859</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3282</v>
+        <v>-3.0465</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8683</v>
+        <v>-2.6666</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4599</v>
+        <v>-0.3799</v>
       </c>
       <c r="G24" t="n">
         <v>-3.8728</v>
@@ -2326,13 +2326,13 @@
         <v>1.7371</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6133999999999999</v>
+        <v>0.6683</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6253</v>
+        <v>0.5764</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0119</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-0.614</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.389699999999999</v>
+        <v>5.101900000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>8.005900000000002</v>
+        <v>8.006</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.6164</v>
+        <v>-2.9041</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7402999999999986</v>
@@ -2404,13 +2404,13 @@
         <v>11.5804</v>
       </c>
       <c r="S25" t="n">
-        <v>7.4956</v>
+        <v>8.207800000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>7.475899999999998</v>
+        <v>7.476099999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0197</v>
+        <v>0.7318</v>
       </c>
       <c r="V25" t="n">
         <v>0.5294000000000002</v>
